--- a/resources/tools/wordlist_E-J/lessons/lesson-21.xlsx
+++ b/resources/tools/wordlist_E-J/lessons/lesson-21.xlsx
@@ -431,216 +431,216 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>baby</t>
+          <t>groper; pervert</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>赤ちゃん|あかちゃん</t>
+          <t>ちかん</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mosquito</t>
+          <t>thief; burglar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>蚊|か</t>
+          <t>泥棒|どろぼう</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>business meeting; conference</t>
+          <t>criminal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>会議|かいぎ</t>
+          <t>犯人|はんにん</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gasoline</t>
+          <t>colleague</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ガソリン</t>
+          <t>同僚|どうりょう</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>business meeting; conference</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>環境|かんきょう</t>
+          <t>会議|かいぎ</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>police; police station</t>
+          <t>speech</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>警察|けいさつ</t>
+          <t>スピーチ</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>factory</t>
+          <t>mosquito</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>工場|こうじょう</t>
+          <t>蚊|か</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>things; matters</t>
+          <t>gasoline</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>事|こと</t>
+          <t>ガソリン</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>last train</t>
+          <t>poster</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>終電|しゅうでん</t>
+          <t>ポスター</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>preparation</t>
+          <t>complaint</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>準備|じゅんび</t>
+          <t>文句|もんく</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>speech</t>
+          <t>absence; not at home</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>スピーチ</t>
+          <t>留守|るす</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>government</t>
+          <t>police; police station</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>政府|せいふ</t>
+          <t>警察|けいさつ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sexual offender; pervert</t>
+          <t>government</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>痴漢|ちかん</t>
+          <t>政府|せいふ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>colleague</t>
+          <t>tuition</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>同僚|どうりょう</t>
+          <t>授業料|じゅぎょうりょう</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>thief; burglar</t>
+          <t>factory</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>泥棒|どろぼう</t>
+          <t>工場|こうじょう</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>abbreviation of アルバイト</t>
+          <t>environment</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>バイト</t>
+          <t>環境|かんきょう</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>criminal</t>
+          <t>last train</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>犯人|はんにん</t>
+          <t>終電|しゅうでん</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>poster</t>
+          <t>things; matters</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ポスター</t>
+          <t>事|こと</t>
         </is>
       </c>
     </row>
@@ -659,151 +659,151 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>complaint</t>
+          <t>far (away)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>文句|もんく</t>
+          <t>遠い|とおい</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>absence; not at home</t>
+          <t>awful</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>留守|るす</t>
+          <t>ひどい</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>to put; to lay; to place</t>
+          <t>safe</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>置く|おく</t>
+          <t>安全|あんぜん（な）</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>to notice</t>
+          <t>messy; disorganized</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>気が付く|きがつく</t>
+          <t>めちゃくちゃ（な）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>to kick</t>
+          <t>strange; unusual</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ける</t>
+          <t>変|へん（な）</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>to bite</t>
+          <t>to put; to lay; to place (place に object を)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>刺す|さす</t>
+          <t>置く|おく</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>to touch</t>
+          <t>to wrap; to cover (～を)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>触る|さわる</t>
+          <t>包む|つつむ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>to be arrested; to be caught</t>
+          <t>to post; to stick (place に object を)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>捕まる|つかまる</t>
+          <t>貼る|はる</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>to wrap; to cover</t>
+          <t>to bake; to burn; to grill (～を)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>包む|つつむ</t>
+          <t>焼く|やく</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>to strike; to hit; to punch</t>
+          <t>to give (to pets, plants, younger siblings, etc.) (～を)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>殴る|なぐる</t>
+          <t>やる</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>to steal; to rob</t>
+          <t>to kick (～を)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>盗む|ぬすむ</t>
+          <t>ける</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>to post; to stick</t>
+          <t>to strike; to hit; to punch (～を)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>貼る|はる</t>
+          <t>殴る|なぐる</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>to step on</t>
+          <t>to step on (～を)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -815,252 +815,252 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>to turn down (somebody); to reject; to jilt</t>
+          <t>to bite (～を)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ふる|振る</t>
+          <t>刺す|さす</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>to complain</t>
+          <t>to steal; to rob (～を)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>文句を言う|もんくをいう</t>
+          <t>盗む|ぬすむ</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>to bake; to burn; to grill</t>
+          <t>to touch (～に／を)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>焼く|やく</t>
+          <t>触る|さわる</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>to give (to pets, plants, younger siblings, etc.)</t>
+          <t>to be arrested; to be caught (～が)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>やる</t>
+          <t>捕まる|つかまる</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>to bully</t>
+          <t>to notice (～に)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>いじめる</t>
+          <t>気が付く|きがつく</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>to change clothes</t>
+          <t>to turn down (somebody); to reject; to jilt (～を)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>着替える|きがえる</t>
+          <t>ふる</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>to save money</t>
+          <t>to complain</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ためる|貯める</t>
+          <t>文句を言う|もんくをいう</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>to continue</t>
+          <t>to bully (～を)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>続ける|つづける</t>
+          <t>いじめる</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>to praise; to say nice things</t>
+          <t>to praise; to say nice things (～を)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ほめる|褒める</t>
+          <t>ほめる</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>to make a mistake</t>
+          <t>to change clothes</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>間違える|まちがえる</t>
+          <t>着替える|きがえる</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>to find</t>
+          <t>to believe (～を)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>見つける|みつける</t>
+          <t>信じる|しんじる</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>to insult; to make a fool of...</t>
+          <t>to save money (～を)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ばかにする|馬鹿にする</t>
+          <t>ためる</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>to be surprised</t>
+          <t>to make a mistake (～を)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>びっくりする</t>
+          <t>間違える|まちがえる</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>to take a nap</t>
+          <t>to find (～を)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>昼寝をする|ひるねをする</t>
+          <t>見つける|みつける</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>to contact</t>
+          <t>to compare (X と Y を)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>連絡する|れんらくする</t>
+          <t>比べる|くらべる</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>far (away)</t>
+          <t>to insult; to make a fool of... (～を)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>遠い|とおい</t>
+          <t>ばかにする</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>awful</t>
+          <t>to be surprised (～に)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ひどい</t>
+          <t>びっくりする</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>safe</t>
+          <t>to take a nap</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>安全|あんぜん（な）</t>
+          <t>昼寝をする|ひるねをする</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>precious; valuable</t>
+          <t>to contact (person に)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>大切|たいせつ（な）</t>
+          <t>連絡する|れんらくする</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>messy; disorganized</t>
+          <t>while...</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>めちゃくちゃ（な）</t>
+          <t>～間に|～あいだに</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>while...</t>
+          <t>in the morning</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>～間に|～あいだに</t>
+          <t>午前中|ごぜんちゅう</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>over sensitive</t>
+          <t>oversensitive</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1631,7 +1631,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>a watch</t>
+          <t>watch; clock</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
